--- a/Team-Data/2012-13/4-16-2012-13.xlsx
+++ b/Team-Data/2012-13/4-16-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" t="n">
         <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>0.543</v>
+        <v>0.55</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J2" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.465</v>
+        <v>0.466</v>
       </c>
       <c r="L2" t="n">
         <v>8.699999999999999</v>
@@ -691,22 +758,22 @@
         <v>23.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="O2" t="n">
         <v>14.1</v>
       </c>
       <c r="P2" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.713</v>
+        <v>0.712</v>
       </c>
       <c r="R2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="S2" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T2" t="n">
         <v>40.7</v>
@@ -721,31 +788,31 @@
         <v>8.1</v>
       </c>
       <c r="X2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z2" t="n">
         <v>18</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>98</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -757,10 +824,10 @@
         <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL2" t="n">
         <v>5</v>
@@ -775,7 +842,7 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
@@ -799,7 +866,7 @@
         <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -808,7 +875,7 @@
         <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>16</v>
@@ -942,7 +1009,7 @@
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
@@ -981,7 +1048,7 @@
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI4" t="n">
         <v>25</v>
@@ -1133,10 +1200,10 @@
         <v>8</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP4" t="n">
         <v>7</v>
@@ -1175,7 +1242,7 @@
         <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -1473,10 +1540,10 @@
         <v>12</v>
       </c>
       <c r="AF6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1728,7 @@
         <v>28</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>20</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1910,7 @@
         <v>17</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2283,7 @@
         <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>21</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2486,7 @@
         <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
         <v>8</v>
@@ -2765,7 +2832,7 @@
         <v>26</v>
       </c>
       <c r="AL13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM13" t="n">
         <v>15</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F14" t="n">
         <v>26</v>
       </c>
       <c r="G14" t="n">
-        <v>0.679</v>
+        <v>0.675</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2875,13 +2942,13 @@
         <v>21.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O14" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P14" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q14" t="n">
         <v>0.711</v>
@@ -2893,10 +2960,10 @@
         <v>30.1</v>
       </c>
       <c r="T14" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U14" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
         <v>14.6</v>
@@ -2911,28 +2978,28 @@
         <v>4.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB14" t="n">
-        <v>101</v>
+        <v>101.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2953,7 +3020,7 @@
         <v>9</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>17</v>
@@ -2965,19 +3032,19 @@
         <v>27</v>
       </c>
       <c r="AR14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2989,7 +3056,7 @@
         <v>4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA14" t="n">
         <v>7</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -3111,19 +3178,19 @@
         <v>12</v>
       </c>
       <c r="AF15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
         <v>16</v>
       </c>
       <c r="AJ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
         <v>10</v>
@@ -3147,7 +3214,7 @@
         <v>30</v>
       </c>
       <c r="AR15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS15" t="n">
         <v>3</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3375,7 @@
         <v>19</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3745,7 @@
         <v>14</v>
       </c>
       <c r="AM18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN18" t="n">
         <v>13</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3912,7 @@
         <v>22</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
@@ -3878,7 +3945,7 @@
         <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT19" t="n">
         <v>14</v>
@@ -3893,7 +3960,7 @@
         <v>6</v>
       </c>
       <c r="AX19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
         <v>24</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4121,7 @@
         <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR20" t="n">
         <v>11</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4276,7 @@
         <v>7</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4497,7 @@
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV22" t="n">
         <v>28</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -4749,10 +4816,10 @@
         <v>19</v>
       </c>
       <c r="AF24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH24" t="n">
         <v>24</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -4961,7 +5028,7 @@
         <v>27</v>
       </c>
       <c r="AP25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ25" t="n">
         <v>20</v>
@@ -4973,7 +5040,7 @@
         <v>22</v>
       </c>
       <c r="AT25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>14</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -5029,31 +5096,31 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E26" t="n">
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G26" t="n">
-        <v>0.407</v>
+        <v>0.413</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K26" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>23.4</v>
@@ -5071,16 +5138,16 @@
         <v>0.776</v>
       </c>
       <c r="R26" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S26" t="n">
         <v>30.1</v>
       </c>
       <c r="T26" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U26" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V26" t="n">
         <v>14.7</v>
@@ -5089,7 +5156,7 @@
         <v>6.6</v>
       </c>
       <c r="X26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y26" t="n">
         <v>4.4</v>
@@ -5098,16 +5165,16 @@
         <v>18.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>-3.1</v>
+        <v>-2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5128,7 +5195,7 @@
         <v>11</v>
       </c>
       <c r="AK26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
         <v>6</v>
@@ -5146,13 +5213,13 @@
         <v>24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT26" t="n">
         <v>23</v>
@@ -5170,13 +5237,13 @@
         <v>26</v>
       </c>
       <c r="AY26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ26" t="n">
         <v>7</v>
       </c>
       <c r="BA26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
         <v>15</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5389,7 @@
         <v>11</v>
       </c>
       <c r="AO27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP27" t="n">
         <v>12</v>
@@ -5355,7 +5422,7 @@
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
         <v>14</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -5575,34 +5642,34 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E29" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F29" t="n">
         <v>48</v>
       </c>
       <c r="G29" t="n">
-        <v>0.407</v>
+        <v>0.4</v>
       </c>
       <c r="H29" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I29" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J29" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L29" t="n">
         <v>6.9</v>
       </c>
       <c r="M29" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N29" t="n">
         <v>0.34</v>
@@ -5611,22 +5678,22 @@
         <v>17.5</v>
       </c>
       <c r="P29" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.788</v>
+        <v>0.787</v>
       </c>
       <c r="R29" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S29" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T29" t="n">
         <v>40.1</v>
       </c>
       <c r="U29" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V29" t="n">
         <v>13.7</v>
@@ -5635,7 +5702,7 @@
         <v>7.3</v>
       </c>
       <c r="X29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y29" t="n">
         <v>4.8</v>
@@ -5647,22 +5714,22 @@
         <v>20.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="AE29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5671,22 +5738,22 @@
         <v>22</v>
       </c>
       <c r="AJ29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
         <v>15</v>
       </c>
       <c r="AM29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN29" t="n">
         <v>26</v>
       </c>
       <c r="AO29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AP29" t="n">
         <v>15</v>
@@ -5704,7 +5771,7 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
@@ -5713,10 +5780,10 @@
         <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5725,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
@@ -6029,13 +6096,13 @@
         <v>23</v>
       </c>
       <c r="AH31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI31" t="n">
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK31" t="n">
         <v>27</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-16-2012-13</t>
+          <t>2013-04-16</t>
         </is>
       </c>
     </row>
